--- a/erp-server/erp-server-wms/src/main/resources/excel/initStock.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/initStock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21210" windowHeight="6660"/>
+    <workbookView windowWidth="21210" windowHeight="7260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,30 +21,6 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>必填</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>非必填，不验证正确性</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -53,19 +29,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>必填，请输入正数</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>必填，仓位编码</t>
+          <t>仓位编码</t>
         </r>
       </text>
     </comment>
@@ -74,15 +38,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>SKU</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>期初数量</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>期初数量</t>
+    </r>
   </si>
   <si>
     <t>仓位</t>
@@ -1071,30 +1070,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="5" max="5" width="21.875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
